--- a/main/ig/CodeSystem-as-cs-organization-types.xlsx
+++ b/main/ig/CodeSystem-as-cs-organization-types.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-04T16:55:03+00:00</t>
+    <t>2024-03-05T15:34:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/CodeSystem-as-cs-organization-types.xlsx
+++ b/main/ig/CodeSystem-as-cs-organization-types.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-05T15:34:40+00:00</t>
+    <t>2024-03-06T10:45:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/CodeSystem-as-cs-organization-types.xlsx
+++ b/main/ig/CodeSystem-as-cs-organization-types.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-06T10:45:14+00:00</t>
+    <t>2024-03-07T10:27:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/CodeSystem-as-cs-organization-types.xlsx
+++ b/main/ig/CodeSystem-as-cs-organization-types.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-07T10:27:01+00:00</t>
+    <t>2024-03-12T12:54:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/CodeSystem-as-cs-organization-types.xlsx
+++ b/main/ig/CodeSystem-as-cs-organization-types.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-12T12:54:34+00:00</t>
+    <t>2024-03-12T13:20:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/CodeSystem-as-cs-organization-types.xlsx
+++ b/main/ig/CodeSystem-as-cs-organization-types.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-12T13:20:54+00:00</t>
+    <t>2024-03-12T13:39:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/CodeSystem-as-cs-organization-types.xlsx
+++ b/main/ig/CodeSystem-as-cs-organization-types.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-12T13:39:01+00:00</t>
+    <t>2024-03-12T13:58:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/CodeSystem-as-cs-organization-types.xlsx
+++ b/main/ig/CodeSystem-as-cs-organization-types.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-12T13:58:30+00:00</t>
+    <t>2024-03-12T14:02:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/CodeSystem-as-cs-organization-types.xlsx
+++ b/main/ig/CodeSystem-as-cs-organization-types.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-12T14:02:45+00:00</t>
+    <t>2024-03-12T14:08:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/CodeSystem-as-cs-organization-types.xlsx
+++ b/main/ig/CodeSystem-as-cs-organization-types.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-12T14:08:02+00:00</t>
+    <t>2024-03-12T14:13:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/CodeSystem-as-cs-organization-types.xlsx
+++ b/main/ig/CodeSystem-as-cs-organization-types.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-12T14:13:18+00:00</t>
+    <t>2024-03-12T14:29:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/CodeSystem-as-cs-organization-types.xlsx
+++ b/main/ig/CodeSystem-as-cs-organization-types.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-12T14:29:58+00:00</t>
+    <t>2024-03-12T16:57:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/CodeSystem-as-cs-organization-types.xlsx
+++ b/main/ig/CodeSystem-as-cs-organization-types.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-12T16:57:02+00:00</t>
+    <t>2024-03-12T17:28:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/CodeSystem-as-cs-organization-types.xlsx
+++ b/main/ig/CodeSystem-as-cs-organization-types.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-12T17:28:16+00:00</t>
+    <t>2024-03-13T08:21:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/CodeSystem-as-cs-organization-types.xlsx
+++ b/main/ig/CodeSystem-as-cs-organization-types.xlsx
@@ -57,13 +57,13 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-13T08:21:45+00:00</t>
+    <t>2024-03-13T15:21:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
   </si>
   <si>
-    <t>ANS</t>
+    <t>Agence du Numérique en Santé (ANS) - 2-10 Rue d'Oradour-sur-Glane, 75015 Paris</t>
   </si>
   <si>
     <t>Contact</t>

--- a/main/ig/CodeSystem-as-cs-organization-types.xlsx
+++ b/main/ig/CodeSystem-as-cs-organization-types.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-13T15:21:15+00:00</t>
+    <t>2024-03-13T15:40:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/CodeSystem-as-cs-organization-types.xlsx
+++ b/main/ig/CodeSystem-as-cs-organization-types.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-13T15:40:01+00:00</t>
+    <t>2024-03-15T14:37:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/CodeSystem-as-cs-organization-types.xlsx
+++ b/main/ig/CodeSystem-as-cs-organization-types.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-02T13:53:07+00:00</t>
+    <t>2024-04-02T14:01:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/CodeSystem-as-cs-organization-types.xlsx
+++ b/main/ig/CodeSystem-as-cs-organization-types.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.0.0-ballot-4</t>
+    <t>1.0.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-02T14:01:28+00:00</t>
+    <t>2024-04-03T13:55:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/CodeSystem-as-cs-organization-types.xlsx
+++ b/main/ig/CodeSystem-as-cs-organization-types.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-08T12:41:20+00:00</t>
+    <t>2024-04-08T12:53:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/CodeSystem-as-cs-organization-types.xlsx
+++ b/main/ig/CodeSystem-as-cs-organization-types.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-08T12:53:48+00:00</t>
+    <t>2024-04-09T07:46:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/CodeSystem-as-cs-organization-types.xlsx
+++ b/main/ig/CodeSystem-as-cs-organization-types.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-09T07:46:55+00:00</t>
+    <t>2024-04-10T12:18:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/CodeSystem-as-cs-organization-types.xlsx
+++ b/main/ig/CodeSystem-as-cs-organization-types.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-10T12:18:24+00:00</t>
+    <t>2024-04-10T12:37:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/CodeSystem-as-cs-organization-types.xlsx
+++ b/main/ig/CodeSystem-as-cs-organization-types.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-10T18:21:45+00:00</t>
+    <t>2024-04-18T13:43:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/CodeSystem-as-cs-organization-types.xlsx
+++ b/main/ig/CodeSystem-as-cs-organization-types.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.0.0</t>
+    <t>1.0.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-18T13:43:00+00:00</t>
+    <t>2024-04-25T11:33:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/CodeSystem-as-cs-organization-types.xlsx
+++ b/main/ig/CodeSystem-as-cs-organization-types.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-03T16:10:14+00:00</t>
+    <t>2024-06-03T16:22:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/CodeSystem-as-cs-organization-types.xlsx
+++ b/main/ig/CodeSystem-as-cs-organization-types.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-03T16:22:01+00:00</t>
+    <t>2024-06-03T16:23:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/CodeSystem-as-cs-organization-types.xlsx
+++ b/main/ig/CodeSystem-as-cs-organization-types.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-03T16:23:50+00:00</t>
+    <t>2024-06-03T16:30:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/CodeSystem-as-cs-organization-types.xlsx
+++ b/main/ig/CodeSystem-as-cs-organization-types.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-03T16:30:34+00:00</t>
+    <t>2024-06-05T12:07:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/CodeSystem-as-cs-organization-types.xlsx
+++ b/main/ig/CodeSystem-as-cs-organization-types.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-05T12:07:44+00:00</t>
+    <t>2024-06-07T15:57:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/CodeSystem-as-cs-organization-types.xlsx
+++ b/main/ig/CodeSystem-as-cs-organization-types.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-07T15:57:22+00:00</t>
+    <t>2024-07-01T19:46:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/CodeSystem-as-cs-organization-types.xlsx
+++ b/main/ig/CodeSystem-as-cs-organization-types.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-01T19:46:33+00:00</t>
+    <t>2024-07-09T08:44:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/CodeSystem-as-cs-organization-types.xlsx
+++ b/main/ig/CodeSystem-as-cs-organization-types.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="51">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-09T08:44:23+00:00</t>
+    <t>2024-07-10T09:54:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -117,7 +117,7 @@
     <t>Count</t>
   </si>
   <si>
-    <t>4</t>
+    <t>5</t>
   </si>
   <si>
     <t>Level</t>
@@ -160,6 +160,12 @@
   </si>
   <si>
     <t>Type d'établissement</t>
+  </si>
+  <si>
+    <t>secteurActiviteRASS</t>
+  </si>
+  <si>
+    <t>Secteur d'activité RASS</t>
   </si>
 </sst>
 </file>
@@ -465,7 +471,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:D5"/>
+  <dimension ref="A1:D6"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -538,6 +544,20 @@
         <v>48</v>
       </c>
     </row>
+    <row r="6">
+      <c r="A6" t="s" s="2">
+        <v>39</v>
+      </c>
+      <c r="B6" t="s" s="2">
+        <v>49</v>
+      </c>
+      <c r="C6" t="s" s="2">
+        <v>50</v>
+      </c>
+      <c r="D6" t="s" s="2">
+        <v>50</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>

--- a/main/ig/CodeSystem-as-cs-organization-types.xlsx
+++ b/main/ig/CodeSystem-as-cs-organization-types.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.0.1</t>
+    <t>1.1.0-snapshot</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-10T09:54:14+00:00</t>
+    <t>2024-07-10T10:00:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/CodeSystem-as-cs-organization-types.xlsx
+++ b/main/ig/CodeSystem-as-cs-organization-types.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-10T10:00:25+00:00</t>
+    <t>2024-07-10T10:02:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/CodeSystem-as-cs-organization-types.xlsx
+++ b/main/ig/CodeSystem-as-cs-organization-types.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-10T10:02:38+00:00</t>
+    <t>2024-07-10T10:13:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/CodeSystem-as-cs-organization-types.xlsx
+++ b/main/ig/CodeSystem-as-cs-organization-types.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-10T10:13:33+00:00</t>
+    <t>2024-07-10T12:01:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/CodeSystem-as-cs-organization-types.xlsx
+++ b/main/ig/CodeSystem-as-cs-organization-types.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-10T12:01:49+00:00</t>
+    <t>2024-07-10T12:37:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/CodeSystem-as-cs-organization-types.xlsx
+++ b/main/ig/CodeSystem-as-cs-organization-types.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-10T12:37:24+00:00</t>
+    <t>2024-07-10T13:09:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/CodeSystem-as-cs-organization-types.xlsx
+++ b/main/ig/CodeSystem-as-cs-organization-types.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-10T13:09:17+00:00</t>
+    <t>2024-07-10T13:09:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/CodeSystem-as-cs-organization-types.xlsx
+++ b/main/ig/CodeSystem-as-cs-organization-types.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-10T13:09:58+00:00</t>
+    <t>2024-07-10T13:27:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/CodeSystem-as-cs-organization-types.xlsx
+++ b/main/ig/CodeSystem-as-cs-organization-types.xlsx
@@ -36,7 +36,7 @@
     <t>Name</t>
   </si>
   <si>
-    <t>AsCsorganizationTypes</t>
+    <t>AsCsOrganizationTypes</t>
   </si>
   <si>
     <t>Title</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-10T13:27:13+00:00</t>
+    <t>2024-07-11T14:15:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/CodeSystem-as-cs-organization-types.xlsx
+++ b/main/ig/CodeSystem-as-cs-organization-types.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="53">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-11T14:15:05+00:00</t>
+    <t>2024-07-11T14:20:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -117,7 +117,7 @@
     <t>Count</t>
   </si>
   <si>
-    <t>5</t>
+    <t>6</t>
   </si>
   <si>
     <t>Level</t>
@@ -133,6 +133,12 @@
   </si>
   <si>
     <t>1</t>
+  </si>
+  <si>
+    <t>organizationType</t>
+  </si>
+  <si>
+    <t>Type d'organisation</t>
   </si>
   <si>
     <t>activiteINSEE</t>
@@ -471,7 +477,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:D6"/>
+  <dimension ref="A1:D7"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -527,7 +533,7 @@
         <v>45</v>
       </c>
       <c r="D4" t="s" s="2">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="5">
@@ -535,10 +541,10 @@
         <v>39</v>
       </c>
       <c r="B5" t="s" s="2">
+        <v>46</v>
+      </c>
+      <c r="C5" t="s" s="2">
         <v>47</v>
-      </c>
-      <c r="C5" t="s" s="2">
-        <v>48</v>
       </c>
       <c r="D5" t="s" s="2">
         <v>48</v>
@@ -556,6 +562,20 @@
       </c>
       <c r="D6" t="s" s="2">
         <v>50</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s" s="2">
+        <v>39</v>
+      </c>
+      <c r="B7" t="s" s="2">
+        <v>51</v>
+      </c>
+      <c r="C7" t="s" s="2">
+        <v>52</v>
+      </c>
+      <c r="D7" t="s" s="2">
+        <v>52</v>
       </c>
     </row>
   </sheetData>

--- a/main/ig/CodeSystem-as-cs-organization-types.xlsx
+++ b/main/ig/CodeSystem-as-cs-organization-types.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.0-snapshot</t>
+    <t>1.1.0-snapshot-2</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-11T14:20:03+00:00</t>
+    <t>2024-07-11T15:32:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/CodeSystem-as-cs-organization-types.xlsx
+++ b/main/ig/CodeSystem-as-cs-organization-types.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-11T15:32:47+00:00</t>
+    <t>2024-07-11T15:43:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/CodeSystem-as-cs-organization-types.xlsx
+++ b/main/ig/CodeSystem-as-cs-organization-types.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-11T15:43:40+00:00</t>
+    <t>2024-07-11T16:04:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/CodeSystem-as-cs-organization-types.xlsx
+++ b/main/ig/CodeSystem-as-cs-organization-types.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-11T16:04:15+00:00</t>
+    <t>2024-07-12T06:54:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/CodeSystem-as-cs-organization-types.xlsx
+++ b/main/ig/CodeSystem-as-cs-organization-types.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-12T06:54:28+00:00</t>
+    <t>2024-07-12T07:24:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/CodeSystem-as-cs-organization-types.xlsx
+++ b/main/ig/CodeSystem-as-cs-organization-types.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-27T17:01:01+00:00</t>
+    <t>2025-01-31T09:33:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/CodeSystem-as-cs-organization-types.xlsx
+++ b/main/ig/CodeSystem-as-cs-organization-types.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-31T09:33:18+00:00</t>
+    <t>2025-02-03T16:26:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/CodeSystem-as-cs-organization-types.xlsx
+++ b/main/ig/CodeSystem-as-cs-organization-types.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-03T16:26:04+00:00</t>
+    <t>2025-02-11T12:19:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/CodeSystem-as-cs-organization-types.xlsx
+++ b/main/ig/CodeSystem-as-cs-organization-types.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-11T12:19:13+00:00</t>
+    <t>2025-02-11T12:46:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/CodeSystem-as-cs-organization-types.xlsx
+++ b/main/ig/CodeSystem-as-cs-organization-types.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-11T12:46:26+00:00</t>
+    <t>2025-02-11T13:37:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/CodeSystem-as-cs-organization-types.xlsx
+++ b/main/ig/CodeSystem-as-cs-organization-types.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-11T13:37:59+00:00</t>
+    <t>2025-02-11T14:09:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/CodeSystem-as-cs-organization-types.xlsx
+++ b/main/ig/CodeSystem-as-cs-organization-types.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-11T14:09:44+00:00</t>
+    <t>2025-02-11T15:57:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/CodeSystem-as-cs-organization-types.xlsx
+++ b/main/ig/CodeSystem-as-cs-organization-types.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-11T15:57:50+00:00</t>
+    <t>2025-02-11T16:04:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/CodeSystem-as-cs-organization-types.xlsx
+++ b/main/ig/CodeSystem-as-cs-organization-types.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-11T16:04:30+00:00</t>
+    <t>2025-02-11T16:35:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/CodeSystem-as-cs-organization-types.xlsx
+++ b/main/ig/CodeSystem-as-cs-organization-types.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-17T22:39:20+00:00</t>
+    <t>2025-02-24T08:37:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/CodeSystem-as-cs-organization-types.xlsx
+++ b/main/ig/CodeSystem-as-cs-organization-types.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-24T08:37:03+00:00</t>
+    <t>2025-02-27T14:21:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/CodeSystem-as-cs-organization-types.xlsx
+++ b/main/ig/CodeSystem-as-cs-organization-types.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-27T14:21:41+00:00</t>
+    <t>2025-02-27T14:23:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/CodeSystem-as-cs-organization-types.xlsx
+++ b/main/ig/CodeSystem-as-cs-organization-types.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-27T14:23:05+00:00</t>
+    <t>2025-02-28T10:02:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/CodeSystem-as-cs-organization-types.xlsx
+++ b/main/ig/CodeSystem-as-cs-organization-types.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-28T10:02:48+00:00</t>
+    <t>2025-03-05T17:59:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/CodeSystem-as-cs-organization-types.xlsx
+++ b/main/ig/CodeSystem-as-cs-organization-types.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-05T17:59:44+00:00</t>
+    <t>2025-03-06T14:41:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/CodeSystem-as-cs-organization-types.xlsx
+++ b/main/ig/CodeSystem-as-cs-organization-types.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-06T14:41:30+00:00</t>
+    <t>2025-03-06T14:56:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/CodeSystem-as-cs-organization-types.xlsx
+++ b/main/ig/CodeSystem-as-cs-organization-types.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-06T14:56:25+00:00</t>
+    <t>2025-03-12T15:24:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/CodeSystem-as-cs-organization-types.xlsx
+++ b/main/ig/CodeSystem-as-cs-organization-types.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-12T15:24:25+00:00</t>
+    <t>2025-03-18T14:02:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/CodeSystem-as-cs-organization-types.xlsx
+++ b/main/ig/CodeSystem-as-cs-organization-types.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-18T14:02:39+00:00</t>
+    <t>2025-03-18T16:59:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/CodeSystem-as-cs-organization-types.xlsx
+++ b/main/ig/CodeSystem-as-cs-organization-types.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-18T16:59:29+00:00</t>
+    <t>2025-03-21T10:50:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/CodeSystem-as-cs-organization-types.xlsx
+++ b/main/ig/CodeSystem-as-cs-organization-types.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.0-snapshot-1</t>
+    <t>1.2.0-snapshot-2</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-18T12:01:00+00:00</t>
+    <t>2026-06-19T13:53:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/CodeSystem-as-cs-organization-types.xlsx
+++ b/main/ig/CodeSystem-as-cs-organization-types.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-19T13:53:04+00:00</t>
+    <t>2026-06-19T14:07:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/CodeSystem-as-cs-organization-types.xlsx
+++ b/main/ig/CodeSystem-as-cs-organization-types.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-19T14:07:56+00:00</t>
+    <t>2026-06-23T09:20:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/CodeSystem-as-cs-organization-types.xlsx
+++ b/main/ig/CodeSystem-as-cs-organization-types.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-23T09:20:47+00:00</t>
+    <t>2026-06-23T12:21:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/CodeSystem-as-cs-organization-types.xlsx
+++ b/main/ig/CodeSystem-as-cs-organization-types.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-23T12:21:55+00:00</t>
+    <t>2026-06-26T10:36:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/CodeSystem-as-cs-organization-types.xlsx
+++ b/main/ig/CodeSystem-as-cs-organization-types.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-26T10:36:05+00:00</t>
+    <t>2026-06-27T10:35:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/CodeSystem-as-cs-organization-types.xlsx
+++ b/main/ig/CodeSystem-as-cs-organization-types.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-27T10:35:23+00:00</t>
+    <t>2026-06-30T07:59:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/CodeSystem-as-cs-organization-types.xlsx
+++ b/main/ig/CodeSystem-as-cs-organization-types.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-30T07:59:11+00:00</t>
+    <t>2026-07-10T15:33:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/CodeSystem-as-cs-organization-types.xlsx
+++ b/main/ig/CodeSystem-as-cs-organization-types.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.0-snapshot-2</t>
+    <t>1.2.0-snapshot-3</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-10T15:33:23+00:00</t>
+    <t>2026-07-10T15:46:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/CodeSystem-as-cs-organization-types.xlsx
+++ b/main/ig/CodeSystem-as-cs-organization-types.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-10T15:46:03+00:00</t>
+    <t>2026-08-03T13:23:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/CodeSystem-as-cs-organization-types.xlsx
+++ b/main/ig/CodeSystem-as-cs-organization-types.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-03T13:23:25+00:00</t>
+    <t>2026-08-03T14:28:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/CodeSystem-as-cs-organization-types.xlsx
+++ b/main/ig/CodeSystem-as-cs-organization-types.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-03T14:28:09+00:00</t>
+    <t>2026-08-04T08:16:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/CodeSystem-as-cs-organization-types.xlsx
+++ b/main/ig/CodeSystem-as-cs-organization-types.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-04T08:16:57+00:00</t>
+    <t>2026-08-04T12:10:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
